--- a/data/DatosGrafica_AdquirirQ1_20260530_195139.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260530_195139.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140187A4-D8EE-4B80-83F5-EDA2B1A1ABBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5F3186-F9CF-48C6-902D-339BDC112675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="2640" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
+        <f>(MAX(B:B)-MIN(B:B))/(MODE(D:D)-MIN(D:D))</f>
         <v>1.1599999999999999</v>
       </c>
       <c r="H2">
@@ -507,12 +507,12 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
-        <v>121</v>
-      </c>
-      <c r="H3">
         <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))*1</f>
         <v>121</v>
+      </c>
+      <c r="H3">
+        <f>0.675*(INDEX(A:A,MATCH(MAX(B:B)*0.853,B:B))-INDEX(A:A,MATCH(MAX(B:B)*0.353,B:B)))</f>
+        <v>197.77500000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -532,12 +532,12 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
-        <v>9</v>
-      </c>
-      <c r="H4">
         <f>INDEX(A:A, MATCH(MIN(B:B)*1.02, B:B)) - (INDEX(A:A, MATCH(MODE(D:D), D:D, 0)))</f>
         <v>9</v>
+      </c>
+      <c r="H4">
+        <f>ABS(1.294*(INDEX(A:A,MATCH(MAX(B:B)*0.353,B:B)))-0.294*(INDEX(A:A,MATCH(MAX(B:B)*0.853,B:B)))-INDEX(A:A,MATCH(MODE(D:D),D:D,0)))</f>
+        <v>65.141999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
